--- a/Demo/CES/demo_ces_9999_1_village.xlsx
+++ b/Demo/CES/demo_ces_9999_1_village.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\CES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5651CD3B-88A4-4442-B803-D67DF6A3AB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B04EDC6-E358-4F01-A1D8-B9DA37FBDC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="519">
   <si>
     <t>type</t>
   </si>
@@ -1292,9 +1292,6 @@
   </si>
   <si>
     <t>Population</t>
-  </si>
-  <si>
-    <t>c_date</t>
   </si>
   <si>
     <t>no</t>
@@ -2094,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -2345,7 +2342,7 @@
         <v>65</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>75</v>
@@ -2386,7 +2383,7 @@
       <c r="F9" s="19"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
@@ -2405,7 +2402,7 @@
         <v>78</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>79</v>
@@ -2415,7 +2412,7 @@
       <c r="F10" s="19"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
@@ -2423,7 +2420,7 @@
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="7"/>
@@ -2446,7 +2443,7 @@
       <c r="F11" s="19"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
@@ -2478,7 +2475,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>42</v>
@@ -2513,7 +2510,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>42</v>
@@ -2593,22 +2590,24 @@
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>418</v>
+        <v>22</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -2622,56 +2621,50 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>24</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10" t="s">
-        <v>42</v>
+        <v>418</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
+      <c r="N18" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>26</v>
-      </c>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="10" t="s">
-        <v>419</v>
-      </c>
+      <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="N19" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -2685,10 +2678,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -2700,24 +2693,6 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5812,10 +5787,10 @@
         <v>323</v>
       </c>
       <c r="B235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E235" t="s">
         <v>147</v>
@@ -5826,10 +5801,10 @@
         <v>323</v>
       </c>
       <c r="B236" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C236" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E236" t="s">
         <v>148</v>
@@ -5840,10 +5815,10 @@
         <v>323</v>
       </c>
       <c r="B237" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C237" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E237" t="s">
         <v>149</v>
@@ -5854,10 +5829,10 @@
         <v>323</v>
       </c>
       <c r="B238" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C238" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E238" t="s">
         <v>150</v>
@@ -5868,10 +5843,10 @@
         <v>323</v>
       </c>
       <c r="B239" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C239" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E239" t="s">
         <v>151</v>
@@ -5882,10 +5857,10 @@
         <v>323</v>
       </c>
       <c r="B240" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C240" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E240" t="s">
         <v>152</v>
@@ -5896,10 +5871,10 @@
         <v>323</v>
       </c>
       <c r="B241" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C241" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E241" t="s">
         <v>153</v>
@@ -5910,10 +5885,10 @@
         <v>323</v>
       </c>
       <c r="B242" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C242" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E242" t="s">
         <v>154</v>
@@ -5924,10 +5899,10 @@
         <v>323</v>
       </c>
       <c r="B243" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C243" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E243" t="s">
         <v>155</v>
@@ -5938,10 +5913,10 @@
         <v>323</v>
       </c>
       <c r="B244" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C244" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E244" t="s">
         <v>156</v>
@@ -5952,10 +5927,10 @@
         <v>323</v>
       </c>
       <c r="B245" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C245" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E245" t="s">
         <v>157</v>
@@ -5966,10 +5941,10 @@
         <v>323</v>
       </c>
       <c r="B246" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C246" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E246" t="s">
         <v>158</v>
@@ -5980,10 +5955,10 @@
         <v>323</v>
       </c>
       <c r="B247" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C247" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E247" t="s">
         <v>159</v>
@@ -5994,10 +5969,10 @@
         <v>323</v>
       </c>
       <c r="B248" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C248" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E248" t="s">
         <v>160</v>
@@ -6008,10 +5983,10 @@
         <v>323</v>
       </c>
       <c r="B249" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C249" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E249" t="s">
         <v>161</v>
@@ -6022,10 +5997,10 @@
         <v>323</v>
       </c>
       <c r="B250" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C250" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E250" t="s">
         <v>162</v>
@@ -6036,10 +6011,10 @@
         <v>323</v>
       </c>
       <c r="B251" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C251" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E251" t="s">
         <v>163</v>
@@ -6050,10 +6025,10 @@
         <v>323</v>
       </c>
       <c r="B252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E252" t="s">
         <v>164</v>
@@ -6064,10 +6039,10 @@
         <v>323</v>
       </c>
       <c r="B253" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C253" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E253" t="s">
         <v>165</v>
@@ -6078,10 +6053,10 @@
         <v>323</v>
       </c>
       <c r="B254" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C254" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E254" t="s">
         <v>166</v>
@@ -6092,10 +6067,10 @@
         <v>323</v>
       </c>
       <c r="B255" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C255" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E255" t="s">
         <v>167</v>
@@ -6106,10 +6081,10 @@
         <v>323</v>
       </c>
       <c r="B256" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C256" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E256" t="s">
         <v>168</v>
@@ -6120,10 +6095,10 @@
         <v>323</v>
       </c>
       <c r="B257" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C257" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E257" t="s">
         <v>169</v>
@@ -6134,10 +6109,10 @@
         <v>323</v>
       </c>
       <c r="B258" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C258" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E258" t="s">
         <v>170</v>
@@ -6148,10 +6123,10 @@
         <v>323</v>
       </c>
       <c r="B259" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C259" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E259" t="s">
         <v>171</v>
@@ -6162,10 +6137,10 @@
         <v>323</v>
       </c>
       <c r="B260" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C260" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E260" t="s">
         <v>172</v>
@@ -6176,10 +6151,10 @@
         <v>323</v>
       </c>
       <c r="B261" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C261" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E261" t="s">
         <v>173</v>
@@ -6190,10 +6165,10 @@
         <v>323</v>
       </c>
       <c r="B262" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C262" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E262" t="s">
         <v>174</v>
@@ -6204,10 +6179,10 @@
         <v>323</v>
       </c>
       <c r="B263" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C263" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E263" t="s">
         <v>175</v>
@@ -6218,10 +6193,10 @@
         <v>323</v>
       </c>
       <c r="B264" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C264" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E264" t="s">
         <v>176</v>
@@ -6232,10 +6207,10 @@
         <v>323</v>
       </c>
       <c r="B265" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C265" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E265" t="s">
         <v>177</v>
@@ -6246,10 +6221,10 @@
         <v>323</v>
       </c>
       <c r="B266" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C266" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E266" t="s">
         <v>178</v>
@@ -6260,10 +6235,10 @@
         <v>323</v>
       </c>
       <c r="B267" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C267" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E267" t="s">
         <v>179</v>
@@ -6274,10 +6249,10 @@
         <v>323</v>
       </c>
       <c r="B268" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C268" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E268" t="s">
         <v>180</v>
@@ -6288,10 +6263,10 @@
         <v>323</v>
       </c>
       <c r="B269" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C269" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E269" t="s">
         <v>181</v>
@@ -6302,10 +6277,10 @@
         <v>323</v>
       </c>
       <c r="B270" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C270" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E270" t="s">
         <v>182</v>
@@ -6316,10 +6291,10 @@
         <v>323</v>
       </c>
       <c r="B271" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C271" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E271" t="s">
         <v>183</v>
@@ -6330,10 +6305,10 @@
         <v>323</v>
       </c>
       <c r="B272" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C272" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E272" t="s">
         <v>184</v>
@@ -6344,10 +6319,10 @@
         <v>323</v>
       </c>
       <c r="B273" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C273" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E273" t="s">
         <v>185</v>
@@ -6358,10 +6333,10 @@
         <v>323</v>
       </c>
       <c r="B274" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C274" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E274" t="s">
         <v>186</v>
@@ -6372,10 +6347,10 @@
         <v>323</v>
       </c>
       <c r="B275" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C275" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E275" t="s">
         <v>187</v>
@@ -6386,10 +6361,10 @@
         <v>323</v>
       </c>
       <c r="B276" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C276" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E276" t="s">
         <v>188</v>
@@ -6400,10 +6375,10 @@
         <v>323</v>
       </c>
       <c r="B277" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C277" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E277" t="s">
         <v>189</v>
@@ -6414,10 +6389,10 @@
         <v>323</v>
       </c>
       <c r="B278" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C278" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E278" t="s">
         <v>190</v>
@@ -6428,10 +6403,10 @@
         <v>323</v>
       </c>
       <c r="B279" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C279" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E279" t="s">
         <v>191</v>
@@ -6442,10 +6417,10 @@
         <v>323</v>
       </c>
       <c r="B280" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C280" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E280" t="s">
         <v>192</v>
@@ -6456,10 +6431,10 @@
         <v>323</v>
       </c>
       <c r="B281" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C281" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E281" t="s">
         <v>193</v>
@@ -6470,10 +6445,10 @@
         <v>323</v>
       </c>
       <c r="B282" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C282" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E282" t="s">
         <v>194</v>
@@ -6484,10 +6459,10 @@
         <v>323</v>
       </c>
       <c r="B283" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C283" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E283" t="s">
         <v>195</v>
@@ -6498,10 +6473,10 @@
         <v>323</v>
       </c>
       <c r="B284" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C284" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E284" t="s">
         <v>196</v>
@@ -6512,10 +6487,10 @@
         <v>323</v>
       </c>
       <c r="B285" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C285" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E285" t="s">
         <v>197</v>
@@ -6526,10 +6501,10 @@
         <v>323</v>
       </c>
       <c r="B286" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C286" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E286" t="s">
         <v>198</v>
@@ -6540,10 +6515,10 @@
         <v>323</v>
       </c>
       <c r="B287" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C287" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E287" t="s">
         <v>199</v>
@@ -6554,10 +6529,10 @@
         <v>323</v>
       </c>
       <c r="B288" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C288" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E288" t="s">
         <v>200</v>
@@ -6568,10 +6543,10 @@
         <v>323</v>
       </c>
       <c r="B289" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C289" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E289" t="s">
         <v>201</v>
@@ -6582,10 +6557,10 @@
         <v>323</v>
       </c>
       <c r="B290" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C290" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E290" t="s">
         <v>202</v>
@@ -6596,10 +6571,10 @@
         <v>323</v>
       </c>
       <c r="B291" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C291" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E291" t="s">
         <v>203</v>
@@ -6610,10 +6585,10 @@
         <v>323</v>
       </c>
       <c r="B292" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C292" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E292" t="s">
         <v>204</v>
@@ -6624,10 +6599,10 @@
         <v>323</v>
       </c>
       <c r="B293" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C293" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E293" t="s">
         <v>205</v>
@@ -6638,10 +6613,10 @@
         <v>323</v>
       </c>
       <c r="B294" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C294" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E294" t="s">
         <v>206</v>
@@ -6652,10 +6627,10 @@
         <v>323</v>
       </c>
       <c r="B295" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C295" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E295" t="s">
         <v>207</v>
@@ -6666,10 +6641,10 @@
         <v>323</v>
       </c>
       <c r="B296" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C296" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E296" t="s">
         <v>208</v>
@@ -6680,10 +6655,10 @@
         <v>323</v>
       </c>
       <c r="B297" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C297" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E297" t="s">
         <v>209</v>
@@ -6694,10 +6669,10 @@
         <v>323</v>
       </c>
       <c r="B298" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C298" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E298" t="s">
         <v>210</v>
@@ -6708,10 +6683,10 @@
         <v>323</v>
       </c>
       <c r="B299" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C299" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E299" t="s">
         <v>211</v>
@@ -6722,10 +6697,10 @@
         <v>323</v>
       </c>
       <c r="B300" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C300" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E300" t="s">
         <v>212</v>
@@ -6736,10 +6711,10 @@
         <v>323</v>
       </c>
       <c r="B301" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C301" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E301" t="s">
         <v>213</v>
@@ -6750,10 +6725,10 @@
         <v>323</v>
       </c>
       <c r="B302" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C302" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E302" t="s">
         <v>214</v>
@@ -6764,10 +6739,10 @@
         <v>323</v>
       </c>
       <c r="B303" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C303" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E303" t="s">
         <v>215</v>
@@ -6778,10 +6753,10 @@
         <v>323</v>
       </c>
       <c r="B304" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C304" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E304" t="s">
         <v>216</v>
@@ -6792,10 +6767,10 @@
         <v>323</v>
       </c>
       <c r="B305" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C305" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E305" t="s">
         <v>217</v>
@@ -6806,10 +6781,10 @@
         <v>323</v>
       </c>
       <c r="B306" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C306" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E306" t="s">
         <v>218</v>
@@ -6820,10 +6795,10 @@
         <v>323</v>
       </c>
       <c r="B307" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C307" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E307" t="s">
         <v>219</v>
@@ -6834,10 +6809,10 @@
         <v>323</v>
       </c>
       <c r="B308" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C308" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E308" t="s">
         <v>220</v>
@@ -6848,10 +6823,10 @@
         <v>323</v>
       </c>
       <c r="B309" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C309" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E309" t="s">
         <v>221</v>
@@ -6862,10 +6837,10 @@
         <v>323</v>
       </c>
       <c r="B310" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C310" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E310" t="s">
         <v>222</v>
@@ -6876,10 +6851,10 @@
         <v>323</v>
       </c>
       <c r="B311" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C311" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E311" t="s">
         <v>223</v>
@@ -6890,10 +6865,10 @@
         <v>323</v>
       </c>
       <c r="B312" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C312" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E312" t="s">
         <v>224</v>
@@ -6904,10 +6879,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C313" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E313" t="s">
         <v>225</v>
@@ -6918,10 +6893,10 @@
         <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C314" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E314" t="s">
         <v>226</v>
@@ -6932,10 +6907,10 @@
         <v>323</v>
       </c>
       <c r="B315" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C315" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E315" t="s">
         <v>227</v>
@@ -6946,10 +6921,10 @@
         <v>323</v>
       </c>
       <c r="B316" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C316" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E316" t="s">
         <v>228</v>
@@ -6960,10 +6935,10 @@
         <v>323</v>
       </c>
       <c r="B317" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C317" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E317" t="s">
         <v>229</v>
@@ -6974,10 +6949,10 @@
         <v>323</v>
       </c>
       <c r="B318" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C318" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E318" t="s">
         <v>230</v>
@@ -6988,10 +6963,10 @@
         <v>323</v>
       </c>
       <c r="B319" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C319" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E319" t="s">
         <v>231</v>
@@ -7002,10 +6977,10 @@
         <v>323</v>
       </c>
       <c r="B320" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C320" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E320" t="s">
         <v>232</v>
@@ -7016,10 +6991,10 @@
         <v>323</v>
       </c>
       <c r="B321" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C321" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E321" t="s">
         <v>233</v>
@@ -8290,10 +8265,10 @@
         <v>414</v>
       </c>
       <c r="B413" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C413" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F413" t="s">
         <v>234</v>
@@ -8304,10 +8279,10 @@
         <v>414</v>
       </c>
       <c r="B414" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C414" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F414" t="s">
         <v>235</v>
@@ -8318,10 +8293,10 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C415" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F415" t="s">
         <v>236</v>
@@ -8332,10 +8307,10 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C416" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F416" t="s">
         <v>237</v>
@@ -8346,10 +8321,10 @@
         <v>414</v>
       </c>
       <c r="B417" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C417" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F417" t="s">
         <v>238</v>
@@ -8360,10 +8335,10 @@
         <v>414</v>
       </c>
       <c r="B418" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C418" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F418" t="s">
         <v>239</v>
@@ -8374,10 +8349,10 @@
         <v>414</v>
       </c>
       <c r="B419" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C419" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F419" t="s">
         <v>240</v>
@@ -8388,10 +8363,10 @@
         <v>414</v>
       </c>
       <c r="B420" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C420" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F420" t="s">
         <v>241</v>
@@ -8402,10 +8377,10 @@
         <v>414</v>
       </c>
       <c r="B421" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C421" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F421" t="s">
         <v>242</v>
@@ -8416,10 +8391,10 @@
         <v>414</v>
       </c>
       <c r="B422" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C422" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F422" t="s">
         <v>243</v>
@@ -8430,10 +8405,10 @@
         <v>414</v>
       </c>
       <c r="B423" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C423" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F423" t="s">
         <v>244</v>
@@ -8444,10 +8419,10 @@
         <v>414</v>
       </c>
       <c r="B424" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C424" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F424" t="s">
         <v>245</v>
@@ -8458,10 +8433,10 @@
         <v>414</v>
       </c>
       <c r="B425" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C425" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F425" t="s">
         <v>246</v>
@@ -8472,10 +8447,10 @@
         <v>414</v>
       </c>
       <c r="B426" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C426" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F426" t="s">
         <v>247</v>
@@ -8486,10 +8461,10 @@
         <v>414</v>
       </c>
       <c r="B427" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C427" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F427" t="s">
         <v>248</v>
@@ -8500,10 +8475,10 @@
         <v>414</v>
       </c>
       <c r="B428" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C428" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F428" t="s">
         <v>249</v>
@@ -8514,10 +8489,10 @@
         <v>414</v>
       </c>
       <c r="B429" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C429" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F429" t="s">
         <v>250</v>
@@ -8528,10 +8503,10 @@
         <v>414</v>
       </c>
       <c r="B430" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C430" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F430" t="s">
         <v>251</v>
@@ -8542,10 +8517,10 @@
         <v>414</v>
       </c>
       <c r="B431" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C431" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F431" t="s">
         <v>252</v>
@@ -8556,10 +8531,10 @@
         <v>414</v>
       </c>
       <c r="B432" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C432" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F432" t="s">
         <v>253</v>
@@ -8570,10 +8545,10 @@
         <v>414</v>
       </c>
       <c r="B433" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C433" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F433" t="s">
         <v>254</v>
@@ -8584,10 +8559,10 @@
         <v>414</v>
       </c>
       <c r="B434" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C434" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F434" t="s">
         <v>255</v>
@@ -8598,10 +8573,10 @@
         <v>414</v>
       </c>
       <c r="B435" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C435" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F435" t="s">
         <v>256</v>
@@ -8612,10 +8587,10 @@
         <v>414</v>
       </c>
       <c r="B436" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C436" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F436" t="s">
         <v>257</v>
@@ -8626,10 +8601,10 @@
         <v>414</v>
       </c>
       <c r="B437" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C437" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F437" t="s">
         <v>258</v>
@@ -8640,10 +8615,10 @@
         <v>414</v>
       </c>
       <c r="B438" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C438" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F438" t="s">
         <v>259</v>
@@ -8654,10 +8629,10 @@
         <v>414</v>
       </c>
       <c r="B439" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C439" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F439" t="s">
         <v>260</v>
@@ -8668,10 +8643,10 @@
         <v>414</v>
       </c>
       <c r="B440" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C440" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F440" t="s">
         <v>261</v>
@@ -8682,10 +8657,10 @@
         <v>414</v>
       </c>
       <c r="B441" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C441" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F441" t="s">
         <v>262</v>
@@ -8696,10 +8671,10 @@
         <v>414</v>
       </c>
       <c r="B442" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C442" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F442" t="s">
         <v>263</v>
@@ -8710,10 +8685,10 @@
         <v>414</v>
       </c>
       <c r="B443" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C443" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F443" t="s">
         <v>264</v>
@@ -8724,10 +8699,10 @@
         <v>414</v>
       </c>
       <c r="B444" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C444" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F444" t="s">
         <v>265</v>
@@ -8738,10 +8713,10 @@
         <v>414</v>
       </c>
       <c r="B445" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C445" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F445" t="s">
         <v>266</v>
@@ -8752,10 +8727,10 @@
         <v>414</v>
       </c>
       <c r="B446" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C446" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F446" t="s">
         <v>267</v>
@@ -8766,10 +8741,10 @@
         <v>414</v>
       </c>
       <c r="B447" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C447" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F447" t="s">
         <v>268</v>
@@ -8780,10 +8755,10 @@
         <v>414</v>
       </c>
       <c r="B448" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C448" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F448" t="s">
         <v>269</v>
@@ -8794,10 +8769,10 @@
         <v>414</v>
       </c>
       <c r="B449" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C449" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F449" t="s">
         <v>270</v>
@@ -8808,10 +8783,10 @@
         <v>414</v>
       </c>
       <c r="B450" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C450" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F450" t="s">
         <v>271</v>
@@ -8822,10 +8797,10 @@
         <v>414</v>
       </c>
       <c r="B451" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C451" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F451" t="s">
         <v>272</v>
@@ -8836,10 +8811,10 @@
         <v>414</v>
       </c>
       <c r="B452" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C452" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F452" t="s">
         <v>273</v>
@@ -8850,10 +8825,10 @@
         <v>414</v>
       </c>
       <c r="B453" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C453" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F453" t="s">
         <v>274</v>
@@ -8864,10 +8839,10 @@
         <v>414</v>
       </c>
       <c r="B454" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C454" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F454" t="s">
         <v>275</v>
@@ -8878,10 +8853,10 @@
         <v>414</v>
       </c>
       <c r="B455" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C455" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F455" t="s">
         <v>276</v>
@@ -8892,10 +8867,10 @@
         <v>414</v>
       </c>
       <c r="B456" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C456" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F456" t="s">
         <v>277</v>
@@ -8906,10 +8881,10 @@
         <v>414</v>
       </c>
       <c r="B457" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C457" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F457" t="s">
         <v>278</v>
@@ -8920,10 +8895,10 @@
         <v>414</v>
       </c>
       <c r="B458" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C458" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F458" t="s">
         <v>279</v>
@@ -8934,10 +8909,10 @@
         <v>414</v>
       </c>
       <c r="B459" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C459" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F459" t="s">
         <v>280</v>
@@ -8948,10 +8923,10 @@
         <v>414</v>
       </c>
       <c r="B460" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C460" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F460" t="s">
         <v>281</v>
@@ -8962,10 +8937,10 @@
         <v>414</v>
       </c>
       <c r="B461" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C461" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F461" t="s">
         <v>282</v>
@@ -8976,10 +8951,10 @@
         <v>414</v>
       </c>
       <c r="B462" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C462" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F462" t="s">
         <v>283</v>
@@ -8990,10 +8965,10 @@
         <v>414</v>
       </c>
       <c r="B463" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C463" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F463" t="s">
         <v>284</v>
@@ -9004,10 +8979,10 @@
         <v>414</v>
       </c>
       <c r="B464" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C464" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F464" t="s">
         <v>285</v>
@@ -9018,10 +8993,10 @@
         <v>414</v>
       </c>
       <c r="B465" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C465" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F465" t="s">
         <v>286</v>
@@ -9032,10 +9007,10 @@
         <v>414</v>
       </c>
       <c r="B466" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C466" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F466" t="s">
         <v>287</v>
@@ -9046,10 +9021,10 @@
         <v>414</v>
       </c>
       <c r="B467" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C467" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F467" t="s">
         <v>288</v>
@@ -9060,10 +9035,10 @@
         <v>414</v>
       </c>
       <c r="B468" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C468" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F468" t="s">
         <v>289</v>
@@ -9074,10 +9049,10 @@
         <v>414</v>
       </c>
       <c r="B469" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C469" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F469" t="s">
         <v>290</v>
@@ -9088,10 +9063,10 @@
         <v>414</v>
       </c>
       <c r="B470" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C470" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F470" t="s">
         <v>291</v>
@@ -9102,10 +9077,10 @@
         <v>414</v>
       </c>
       <c r="B471" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C471" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F471" t="s">
         <v>292</v>
@@ -9116,10 +9091,10 @@
         <v>414</v>
       </c>
       <c r="B472" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C472" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F472" t="s">
         <v>293</v>
@@ -9130,10 +9105,10 @@
         <v>414</v>
       </c>
       <c r="B473" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C473" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F473" t="s">
         <v>294</v>
@@ -9144,10 +9119,10 @@
         <v>414</v>
       </c>
       <c r="B474" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C474" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F474" t="s">
         <v>295</v>
@@ -9158,10 +9133,10 @@
         <v>414</v>
       </c>
       <c r="B475" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C475" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F475" t="s">
         <v>296</v>
@@ -9172,10 +9147,10 @@
         <v>414</v>
       </c>
       <c r="B476" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C476" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F476" t="s">
         <v>297</v>
@@ -9186,10 +9161,10 @@
         <v>414</v>
       </c>
       <c r="B477" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C477" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F477" t="s">
         <v>298</v>
@@ -9200,10 +9175,10 @@
         <v>414</v>
       </c>
       <c r="B478" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C478" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F478" t="s">
         <v>299</v>
@@ -9214,10 +9189,10 @@
         <v>414</v>
       </c>
       <c r="B479" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C479" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F479" t="s">
         <v>300</v>
@@ -9228,10 +9203,10 @@
         <v>414</v>
       </c>
       <c r="B480" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C480" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F480" t="s">
         <v>301</v>
@@ -9242,10 +9217,10 @@
         <v>414</v>
       </c>
       <c r="B481" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C481" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F481" t="s">
         <v>302</v>
@@ -9256,10 +9231,10 @@
         <v>414</v>
       </c>
       <c r="B482" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C482" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F482" t="s">
         <v>303</v>
@@ -9270,10 +9245,10 @@
         <v>414</v>
       </c>
       <c r="B483" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C483" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F483" t="s">
         <v>304</v>
@@ -9284,10 +9259,10 @@
         <v>414</v>
       </c>
       <c r="B484" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C484" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F484" t="s">
         <v>305</v>
@@ -9298,10 +9273,10 @@
         <v>414</v>
       </c>
       <c r="B485" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C485" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F485" t="s">
         <v>306</v>
@@ -9312,10 +9287,10 @@
         <v>414</v>
       </c>
       <c r="B486" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C486" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F486" t="s">
         <v>307</v>
@@ -9326,10 +9301,10 @@
         <v>414</v>
       </c>
       <c r="B487" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C487" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F487" t="s">
         <v>308</v>
@@ -9340,10 +9315,10 @@
         <v>414</v>
       </c>
       <c r="B488" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C488" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F488" t="s">
         <v>309</v>
@@ -9354,10 +9329,10 @@
         <v>414</v>
       </c>
       <c r="B489" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C489" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F489" t="s">
         <v>310</v>
@@ -9368,10 +9343,10 @@
         <v>414</v>
       </c>
       <c r="B490" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F490" t="s">
         <v>311</v>
@@ -9382,10 +9357,10 @@
         <v>414</v>
       </c>
       <c r="B491" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C491" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F491" t="s">
         <v>312</v>
@@ -9396,10 +9371,10 @@
         <v>414</v>
       </c>
       <c r="B492" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C492" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F492" t="s">
         <v>313</v>
@@ -9410,10 +9385,10 @@
         <v>414</v>
       </c>
       <c r="B493" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C493" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F493" t="s">
         <v>314</v>
@@ -9424,10 +9399,10 @@
         <v>414</v>
       </c>
       <c r="B494" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C494" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F494" t="s">
         <v>315</v>
@@ -9438,10 +9413,10 @@
         <v>414</v>
       </c>
       <c r="B495" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C495" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F495" t="s">
         <v>316</v>
@@ -9452,10 +9427,10 @@
         <v>414</v>
       </c>
       <c r="B496" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C496" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F496" t="s">
         <v>317</v>
@@ -9466,10 +9441,10 @@
         <v>414</v>
       </c>
       <c r="B497" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C497" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F497" t="s">
         <v>318</v>
@@ -9480,10 +9455,10 @@
         <v>414</v>
       </c>
       <c r="B498" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C498" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F498" t="s">
         <v>319</v>
@@ -9494,10 +9469,10 @@
         <v>414</v>
       </c>
       <c r="B499" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C499" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F499" t="s">
         <v>320</v>
@@ -9508,10 +9483,10 @@
         <v>414</v>
       </c>
       <c r="B500" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C500" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F500" t="s">
         <v>321</v>
@@ -9522,10 +9497,10 @@
         <v>414</v>
       </c>
       <c r="B501" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C501" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F501" t="s">
         <v>322</v>
@@ -10793,13 +10768,13 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B594">
         <v>101</v>
       </c>
       <c r="C594" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E594" t="s">
         <v>189</v>
@@ -10810,13 +10785,13 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B595">
         <v>102</v>
       </c>
       <c r="C595" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E595" t="s">
         <v>189</v>
@@ -10827,13 +10802,13 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B596">
         <v>103</v>
       </c>
       <c r="C596" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E596" t="s">
         <v>189</v>
@@ -10844,13 +10819,13 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B597">
         <v>104</v>
       </c>
       <c r="C597" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E597" t="s">
         <v>190</v>
@@ -10861,13 +10836,13 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B598">
         <v>105</v>
       </c>
       <c r="C598" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E598" t="s">
         <v>190</v>
@@ -10878,13 +10853,13 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B599">
         <v>106</v>
       </c>
       <c r="C599" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E599" t="s">
         <v>191</v>
@@ -10895,13 +10870,13 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B600">
         <v>107</v>
       </c>
       <c r="C600" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E600" t="s">
         <v>193</v>
@@ -10912,13 +10887,13 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B601">
         <v>108</v>
       </c>
       <c r="C601" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E601" t="s">
         <v>194</v>
@@ -10929,13 +10904,13 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B602">
         <v>109</v>
       </c>
       <c r="C602" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E602" t="s">
         <v>195</v>
@@ -10946,13 +10921,13 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B603">
         <v>110</v>
       </c>
       <c r="C603" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E603" t="s">
         <v>192</v>
@@ -10963,13 +10938,13 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B604">
         <v>111</v>
       </c>
       <c r="C604" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E604" t="s">
         <v>175</v>
@@ -10980,13 +10955,13 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B605">
         <v>112</v>
       </c>
       <c r="C605" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E605" t="s">
         <v>174</v>
@@ -10997,13 +10972,13 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B606">
         <v>113</v>
       </c>
       <c r="C606" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E606" t="s">
         <v>173</v>
@@ -11014,13 +10989,13 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B607">
         <v>114</v>
       </c>
       <c r="C607" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E607" t="s">
         <v>201</v>
@@ -11031,13 +11006,13 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B608">
         <v>115</v>
       </c>
       <c r="C608" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E608" t="s">
         <v>202</v>
@@ -11048,13 +11023,13 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B609">
         <v>116</v>
       </c>
       <c r="C609" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E609" t="s">
         <v>177</v>
@@ -11065,13 +11040,13 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B610">
         <v>117</v>
       </c>
       <c r="C610" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E610" t="s">
         <v>176</v>
@@ -11082,13 +11057,13 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B611">
         <v>118</v>
       </c>
       <c r="C611" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E611" t="s">
         <v>178</v>
@@ -11099,13 +11074,13 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B612">
         <v>119</v>
       </c>
       <c r="C612" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E612" t="s">
         <v>227</v>
@@ -11116,13 +11091,13 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B613">
         <v>120</v>
       </c>
       <c r="C613" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E613" t="s">
         <v>226</v>
@@ -11133,13 +11108,13 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B614">
         <v>121</v>
       </c>
       <c r="C614" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E614" t="s">
         <v>209</v>
@@ -11150,13 +11125,13 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B615">
         <v>122</v>
       </c>
       <c r="C615" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E615" t="s">
         <v>223</v>
@@ -11167,13 +11142,13 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B616">
         <v>123</v>
       </c>
       <c r="C616" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E616" t="s">
         <v>186</v>
@@ -11184,13 +11159,13 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B617">
         <v>124</v>
       </c>
       <c r="C617" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E617" t="s">
         <v>187</v>
@@ -11201,13 +11176,13 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B618">
         <v>125</v>
       </c>
       <c r="C618" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E618" t="s">
         <v>188</v>
@@ -11218,13 +11193,13 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B619">
         <v>126</v>
       </c>
       <c r="C619" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E619" t="s">
         <v>198</v>
@@ -11235,13 +11210,13 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B620">
         <v>127</v>
       </c>
       <c r="C620" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E620" t="s">
         <v>199</v>
@@ -11252,13 +11227,13 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B621">
         <v>128</v>
       </c>
       <c r="C621" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E621" t="s">
         <v>197</v>
@@ -11269,13 +11244,13 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B622">
         <v>129</v>
       </c>
       <c r="C622" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E622" t="s">
         <v>182</v>
@@ -11286,13 +11261,13 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B623">
         <v>130</v>
       </c>
       <c r="C623" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E623" t="s">
         <v>181</v>
@@ -11303,13 +11278,13 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B624">
         <v>131</v>
       </c>
       <c r="C624" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E624" t="s">
         <v>180</v>
@@ -11320,13 +11295,13 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B625">
         <v>132</v>
       </c>
       <c r="C625" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E625" t="s">
         <v>179</v>
@@ -11337,13 +11312,13 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B626">
         <v>133</v>
       </c>
       <c r="C626" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E626" t="s">
         <v>212</v>
@@ -11354,13 +11329,13 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B627">
         <v>134</v>
       </c>
       <c r="C627" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E627" t="s">
         <v>213</v>
@@ -11371,13 +11346,13 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B628">
         <v>135</v>
       </c>
       <c r="C628" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E628" t="s">
         <v>150</v>
@@ -11388,13 +11363,13 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B629">
         <v>136</v>
       </c>
       <c r="C629" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E629" t="s">
         <v>151</v>
@@ -11405,13 +11380,13 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B630">
         <v>137</v>
       </c>
       <c r="C630" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E630" t="s">
         <v>171</v>
@@ -11422,13 +11397,13 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B631">
         <v>138</v>
       </c>
       <c r="C631" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E631" t="s">
         <v>172</v>
@@ -11439,13 +11414,13 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B632">
         <v>139</v>
       </c>
       <c r="C632" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E632" t="s">
         <v>217</v>
@@ -11456,13 +11431,13 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B633">
         <v>140</v>
       </c>
       <c r="C633" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E633" t="s">
         <v>216</v>
@@ -11473,13 +11448,13 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B634">
         <v>141</v>
       </c>
       <c r="C634" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E634" t="s">
         <v>156</v>
@@ -11490,13 +11465,13 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B635">
         <v>142</v>
       </c>
       <c r="C635" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E635" t="s">
         <v>155</v>
@@ -11507,13 +11482,13 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B636">
         <v>143</v>
       </c>
       <c r="C636" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E636" t="s">
         <v>165</v>
@@ -11524,13 +11499,13 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B637">
         <v>144</v>
       </c>
       <c r="C637" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E637" t="s">
         <v>166</v>
@@ -11541,13 +11516,13 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B638">
         <v>145</v>
       </c>
       <c r="C638" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E638" t="s">
         <v>230</v>
@@ -11558,13 +11533,13 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B639">
         <v>146</v>
       </c>
       <c r="C639" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E639" t="s">
         <v>229</v>
@@ -11575,13 +11550,13 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B640">
         <v>147</v>
       </c>
       <c r="C640" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E640" t="s">
         <v>162</v>
@@ -11592,13 +11567,13 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B641">
         <v>148</v>
       </c>
       <c r="C641" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E641" t="s">
         <v>163</v>
@@ -11609,13 +11584,13 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B642">
         <v>149</v>
       </c>
       <c r="C642" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E642" t="s">
         <v>149</v>
@@ -11626,13 +11601,13 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B643">
         <v>150</v>
       </c>
       <c r="C643" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E643" t="s">
         <v>206</v>
@@ -11643,13 +11618,13 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B644">
         <v>151</v>
       </c>
       <c r="C644" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E644" t="s">
         <v>185</v>
@@ -11660,13 +11635,13 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B645">
         <v>152</v>
       </c>
       <c r="C645" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E645" t="s">
         <v>184</v>
@@ -11677,13 +11652,13 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B646">
         <v>153</v>
       </c>
       <c r="C646" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E646" t="s">
         <v>168</v>
@@ -11694,13 +11669,13 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B647">
         <v>154</v>
       </c>
       <c r="C647" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E647" t="s">
         <v>161</v>
@@ -11711,13 +11686,13 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B648">
         <v>155</v>
       </c>
       <c r="C648" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E648" t="s">
         <v>160</v>
@@ -11728,13 +11703,13 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B649">
         <v>156</v>
       </c>
       <c r="C649" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E649" t="s">
         <v>203</v>
@@ -11745,13 +11720,13 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B650">
         <v>157</v>
       </c>
       <c r="C650" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E650" t="s">
         <v>221</v>
@@ -11762,13 +11737,13 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B651">
         <v>158</v>
       </c>
       <c r="C651" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E651" t="s">
         <v>204</v>
@@ -11779,13 +11754,13 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B652">
         <v>159</v>
       </c>
       <c r="C652" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E652" t="s">
         <v>218</v>
@@ -11796,13 +11771,13 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B653">
         <v>160</v>
       </c>
       <c r="C653" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E653" t="s">
         <v>207</v>
@@ -11813,13 +11788,13 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B654">
         <v>161</v>
       </c>
       <c r="C654" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E654" t="s">
         <v>169</v>
@@ -11830,13 +11805,13 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B655">
         <v>162</v>
       </c>
       <c r="C655" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E655" t="s">
         <v>170</v>
@@ -11847,13 +11822,13 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B656">
         <v>163</v>
       </c>
       <c r="C656" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E656" t="s">
         <v>196</v>
@@ -11864,13 +11839,13 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B657">
         <v>164</v>
       </c>
       <c r="C657" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E657" t="s">
         <v>231</v>
@@ -11881,13 +11856,13 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B658">
         <v>165</v>
       </c>
       <c r="C658" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E658" t="s">
         <v>167</v>
@@ -11898,13 +11873,13 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B659">
         <v>166</v>
       </c>
       <c r="C659" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E659" t="s">
         <v>148</v>
@@ -11915,13 +11890,13 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B660">
         <v>167</v>
       </c>
       <c r="C660" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E660" t="s">
         <v>211</v>
@@ -11932,13 +11907,13 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B661">
         <v>168</v>
       </c>
       <c r="C661" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E661" t="s">
         <v>225</v>
@@ -11949,13 +11924,13 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B662">
         <v>169</v>
       </c>
       <c r="C662" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E662" t="s">
         <v>219</v>
@@ -11966,13 +11941,13 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B663">
         <v>170</v>
       </c>
       <c r="C663" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E663" t="s">
         <v>183</v>
@@ -11983,13 +11958,13 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B664">
         <v>171</v>
       </c>
       <c r="C664" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E664" t="s">
         <v>164</v>
@@ -12000,13 +11975,13 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B665">
         <v>172</v>
       </c>
       <c r="C665" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E665" t="s">
         <v>157</v>
@@ -12017,13 +11992,13 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B666">
         <v>173</v>
       </c>
       <c r="C666" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E666" t="s">
         <v>158</v>
@@ -12034,13 +12009,13 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B667">
         <v>174</v>
       </c>
       <c r="C667" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E667" t="s">
         <v>232</v>
@@ -12051,13 +12026,13 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B668">
         <v>175</v>
       </c>
       <c r="C668" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E668" t="s">
         <v>210</v>
@@ -12068,13 +12043,13 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B669">
         <v>176</v>
       </c>
       <c r="C669" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E669" t="s">
         <v>153</v>
@@ -12085,13 +12060,13 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B670">
         <v>177</v>
       </c>
       <c r="C670" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E670" t="s">
         <v>228</v>
@@ -12102,13 +12077,13 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B671">
         <v>178</v>
       </c>
       <c r="C671" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E671" t="s">
         <v>214</v>
@@ -12119,13 +12094,13 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B672">
         <v>179</v>
       </c>
       <c r="C672" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E672" t="s">
         <v>152</v>
@@ -12136,13 +12111,13 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B673">
         <v>180</v>
       </c>
       <c r="C673" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E673" t="s">
         <v>147</v>
@@ -12153,13 +12128,13 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B674">
         <v>181</v>
       </c>
       <c r="C674" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E674" t="s">
         <v>220</v>
@@ -12170,13 +12145,13 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B675">
         <v>182</v>
       </c>
       <c r="C675" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E675" t="s">
         <v>215</v>
@@ -12187,13 +12162,13 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B676">
         <v>183</v>
       </c>
       <c r="C676" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E676" t="s">
         <v>233</v>
@@ -12204,13 +12179,13 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B677">
         <v>184</v>
       </c>
       <c r="C677" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E677" t="s">
         <v>205</v>
@@ -12221,13 +12196,13 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B678">
         <v>185</v>
       </c>
       <c r="C678" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E678" t="s">
         <v>224</v>
@@ -12238,13 +12213,13 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B679">
         <v>186</v>
       </c>
       <c r="C679" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E679" t="s">
         <v>154</v>
@@ -12255,13 +12230,13 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B680">
         <v>187</v>
       </c>
       <c r="C680" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E680" t="s">
         <v>159</v>
@@ -12272,13 +12247,13 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B681">
         <v>188</v>
       </c>
       <c r="C681" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E681" t="s">
         <v>200</v>
@@ -12289,13 +12264,13 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B682">
         <v>189</v>
       </c>
       <c r="C682" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E682" t="s">
         <v>208</v>
@@ -12306,13 +12281,13 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B683">
         <v>190</v>
       </c>
       <c r="C683" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E683" t="s">
         <v>222</v>
@@ -12348,7 +12323,7 @@
         <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">

--- a/Demo/CES/demo_ces_9999_1_village.xlsx
+++ b/Demo/CES/demo_ces_9999_1_village.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\CES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B04EDC6-E358-4F01-A1D8-B9DA37FBDC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B34CCC-6585-4C64-8977-892AE86C44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -2096,7 +2096,7 @@
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.85546875" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -2106,7 +2106,7 @@
     <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="11.5703125" customWidth="1"/>
-    <col min="14" max="16" width="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="16" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
